--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8175,0.1311,0.0724,0.0016</t>
-  </si>
-  <si>
-    <t>0.8925,0.0397,0.0317,0.0047</t>
-  </si>
-  <si>
-    <t>0.8159,0.0954,0.0507,0.0093</t>
-  </si>
-  <si>
-    <t>0.7595,0.2255,0.0294,0.0028</t>
-  </si>
-  <si>
-    <t>0.8315,0.0648,0.0304,0.0105</t>
-  </si>
-  <si>
-    <t>0.8099,0.0273,0.0106,0.0306</t>
-  </si>
-  <si>
-    <t>0.8611,0.0459,0.0169,0.0067</t>
-  </si>
-  <si>
-    <t>0.8313,0.0724,0.0231,0.0084</t>
-  </si>
-  <si>
-    <t>0.8550,0.0211,0.0212,0.0228</t>
-  </si>
-  <si>
-    <t>0.6989,0.2079,0.0589,0.0096</t>
-  </si>
-  <si>
-    <t>0.7481,0.1351,0.0516,0.0135</t>
-  </si>
-  <si>
-    <t>0.6654,0.2276,0.0602,0.0130</t>
-  </si>
-  <si>
-    <t>0.9303,0.0347,0.0258,0.0004</t>
-  </si>
-  <si>
-    <t>0.9398,0.0261,0.0266,0.0002</t>
-  </si>
-  <si>
-    <t>0.9310,0.0265,0.0368,0.0006</t>
-  </si>
-  <si>
-    <t>0.9507,0.0118,0.0293,0.0001</t>
-  </si>
-  <si>
-    <t>0.9361,0.0237,0.0276,0.0009</t>
-  </si>
-  <si>
-    <t>0.5931,0.4628,0.0877,0.0010</t>
-  </si>
-  <si>
-    <t>0.4570,0.6575,0.0713,0.0019</t>
-  </si>
-  <si>
-    <t>0.7249,0.1822,0.0543,0.0095</t>
-  </si>
-  <si>
-    <t>0.3095,0.7801,0.1065,0.0024</t>
-  </si>
-  <si>
-    <t>0.2982,0.7822,0.0683,0.0011</t>
-  </si>
-  <si>
-    <t>0.9764,0.0031,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.9454,0.0143,0.0355,0.0007</t>
-  </si>
-  <si>
-    <t>0.8378,0.0088,0.1700,0.0009</t>
-  </si>
-  <si>
-    <t>0.9578,0.0025,0.0368,0.0003</t>
-  </si>
-  <si>
-    <t>0.8858,0.0115,0.1279,0.0003</t>
-  </si>
-  <si>
-    <t>0.9028,0.0145,0.0796,0.0005</t>
-  </si>
-  <si>
-    <t>0.5460,0.0895,0.4848,0.0054</t>
-  </si>
-  <si>
-    <t>0.8914,0.0826,0.0189,0.0016</t>
-  </si>
-  <si>
-    <t>0.8989,0.0871,0.0244,0.0002</t>
-  </si>
-  <si>
-    <t>0.2291,0.1457,0.7523,0.0035</t>
-  </si>
-  <si>
-    <t>0.6223,0.2985,0.1520,0.0007</t>
-  </si>
-  <si>
-    <t>0.8238,0.1296,0.0467,0.0034</t>
-  </si>
-  <si>
-    <t>0.7823,0.0547,0.1625,0.0058</t>
-  </si>
-  <si>
-    <t>0.6582,0.2941,0.0860,0.0044</t>
-  </si>
-  <si>
-    <t>0.8868,0.0891,0.0301,0.0013</t>
-  </si>
-  <si>
-    <t>0.7979,0.1077,0.0439,0.0008</t>
-  </si>
-  <si>
-    <t>0.9703,0.0012,0.0290,0.0000</t>
-  </si>
-  <si>
-    <t>0.9711,0.0028,0.0178,0.0003</t>
-  </si>
-  <si>
-    <t>0.9735,0.0101,0.0132,0.0001</t>
-  </si>
-  <si>
-    <t>0.9310,0.0035,0.0966,0.0001</t>
-  </si>
-  <si>
-    <t>0.7409,0.3565,0.0094,0.0001</t>
-  </si>
-  <si>
-    <t>0.9101,0.0068,0.1064,0.0004</t>
-  </si>
-  <si>
-    <t>0.9333,0.0493,0.0164,0.0005</t>
-  </si>
-  <si>
-    <t>0.1363,0.9113,0.0421,0.0002</t>
-  </si>
-  <si>
-    <t>0.3162,0.8126,0.0412,0.0001</t>
-  </si>
-  <si>
-    <t>0.4769,0.6838,0.0333,0.0006</t>
-  </si>
-  <si>
-    <t>0.8047,0.0142,0.2176,0.0005</t>
-  </si>
-  <si>
-    <t>0.8015,0.0141,0.2575,0.0006</t>
-  </si>
-  <si>
-    <t>0.9345,0.0071,0.0677,0.0004</t>
-  </si>
-  <si>
-    <t>0.9678,0.0047,0.0209,0.0001</t>
-  </si>
-  <si>
-    <t>0.7425,0.0124,0.3966,0.0005</t>
-  </si>
-  <si>
-    <t>0.9584,0.0025,0.0461,0.0001</t>
-  </si>
-  <si>
-    <t>0.8703,0.0907,0.0280,0.0025</t>
-  </si>
-  <si>
-    <t>0.7516,0.1595,0.0451,0.0078</t>
-  </si>
-  <si>
-    <t>0.7717,0.0897,0.0342,0.0175</t>
-  </si>
-  <si>
-    <t>0.5965,0.1822,0.3523,0.0041</t>
-  </si>
-  <si>
-    <t>0.6379,0.1516,0.0332,0.0190</t>
-  </si>
-  <si>
-    <t>0.8453,0.0931,0.0238,0.0038</t>
-  </si>
-  <si>
-    <t>0.8377,0.0557,0.0227,0.0080</t>
-  </si>
-  <si>
-    <t>0.6474,0.1151,0.1634,0.0006</t>
-  </si>
-  <si>
-    <t>0.8165,0.0256,0.1680,0.0002</t>
-  </si>
-  <si>
-    <t>0.8001,0.0230,0.1968,0.0005</t>
-  </si>
-  <si>
-    <t>0.6148,0.2434,0.0967,0.0004</t>
-  </si>
-  <si>
-    <t>0.5923,0.0188,0.5326,0.0007</t>
-  </si>
-  <si>
-    <t>0.6974,0.3548,0.0591,0.0023</t>
-  </si>
-  <si>
-    <t>0.2098,0.8643,0.0141,0.0004</t>
-  </si>
-  <si>
-    <t>0.8239,0.1123,0.1005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9805,0.0150,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.2535,0.3618,0.6669,0.0067</t>
-  </si>
-  <si>
-    <t>0.7248,0.2033,0.0409,0.0001</t>
-  </si>
-  <si>
-    <t>0.8422,0.0608,0.0653,0.0001</t>
-  </si>
-  <si>
-    <t>0.2321,0.8714,0.0091,0.0000</t>
-  </si>
-  <si>
-    <t>0.3139,0.4607,0.1528,0.0002</t>
-  </si>
-  <si>
-    <t>0.8843,0.0584,0.0296,0.0020</t>
-  </si>
-  <si>
-    <t>0.8232,0.0987,0.0315,0.0065</t>
-  </si>
-  <si>
-    <t>0.9709,0.0141,0.0061,0.0005</t>
-  </si>
-  <si>
-    <t>0.8908,0.0757,0.0231,0.0022</t>
-  </si>
-  <si>
-    <t>0.9191,0.0283,0.0144,0.0034</t>
-  </si>
-  <si>
-    <t>0.9135,0.0539,0.0184,0.0022</t>
-  </si>
-  <si>
-    <t>0.8198,0.1146,0.0399,0.0001</t>
-  </si>
-  <si>
-    <t>0.7055,0.0381,0.2935,0.0003</t>
-  </si>
-  <si>
-    <t>0.6935,0.1622,0.0978,0.0005</t>
-  </si>
-  <si>
-    <t>0.8912,0.0196,0.0909,0.0005</t>
-  </si>
-  <si>
-    <t>0.8837,0.0079,0.1635,0.0002</t>
-  </si>
-  <si>
-    <t>0.7575,0.0962,0.0739,0.0001</t>
-  </si>
-  <si>
-    <t>0.7859,0.0726,0.0274,0.0179</t>
-  </si>
-  <si>
-    <t>0.8822,0.0309,0.0170,0.0086</t>
-  </si>
-  <si>
-    <t>0.8416,0.0390,0.0350,0.0114</t>
-  </si>
-  <si>
-    <t>0.7732,0.1023,0.0383,0.0113</t>
-  </si>
-  <si>
-    <t>0.7869,0.0778,0.0304,0.0117</t>
-  </si>
-  <si>
-    <t>0.7994,0.0579,0.0254,0.0154</t>
-  </si>
-  <si>
-    <t>0.7919,0.0562,0.0256,0.0181</t>
-  </si>
-  <si>
-    <t>0.7142,0.1085,0.0497,0.0212</t>
-  </si>
-  <si>
-    <t>0.7390,0.0894,0.0406,0.0235</t>
-  </si>
-  <si>
-    <t>0.8519,0.0544,0.0454,0.0085</t>
-  </si>
-  <si>
-    <t>0.7126,0.0345,0.0136,0.0542</t>
-  </si>
-  <si>
-    <t>0.8493,0.0648,0.0195,0.0117</t>
-  </si>
-  <si>
-    <t>0.8384,0.0872,0.0431,0.0033</t>
-  </si>
-  <si>
-    <t>0.8120,0.0485,0.0170,0.0171</t>
-  </si>
-  <si>
-    <t>0.7738,0.1037,0.0380,0.0129</t>
-  </si>
-  <si>
-    <t>0.8489,0.0445,0.0205,0.0121</t>
-  </si>
-  <si>
-    <t>0.1778,0.0351,0.8609,0.0045</t>
-  </si>
-  <si>
-    <t>0.9409,0.0126,0.0398,0.0001</t>
-  </si>
-  <si>
-    <t>0.9479,0.0235,0.0234,0.0001</t>
-  </si>
-  <si>
-    <t>0.8822,0.0067,0.1518,0.0003</t>
-  </si>
-  <si>
-    <t>0.6502,0.4034,0.0645,0.0014</t>
-  </si>
-  <si>
-    <t>0.2401,0.8531,0.0602,0.0013</t>
-  </si>
-  <si>
-    <t>0.7184,0.2153,0.0476,0.0046</t>
-  </si>
-  <si>
-    <t>0.6471,0.3144,0.0482,0.0035</t>
-  </si>
-  <si>
-    <t>0.7808,0.2073,0.0436,0.0024</t>
-  </si>
-  <si>
-    <t>0.7012,0.3876,0.0350,0.0011</t>
-  </si>
-  <si>
-    <t>0.5452,0.5400,0.0881,0.0027</t>
-  </si>
-  <si>
-    <t>0.8831,0.0806,0.0390,0.0011</t>
-  </si>
-  <si>
-    <t>0.9379,0.0145,0.0399,0.0004</t>
-  </si>
-  <si>
-    <t>0.8960,0.0693,0.0355,0.0002</t>
-  </si>
-  <si>
-    <t>0.8474,0.1608,0.0279,0.0006</t>
-  </si>
-  <si>
-    <t>0.8771,0.0496,0.0762,0.0009</t>
-  </si>
-  <si>
-    <t>0.2165,0.9091,0.0232,0.0004</t>
-  </si>
-  <si>
-    <t>0.7974,0.3225,0.0182,0.0002</t>
-  </si>
-  <si>
-    <t>0.7723,0.2770,0.0418,0.0005</t>
-  </si>
-  <si>
-    <t>0.0558,0.9545,0.1044,0.0007</t>
-  </si>
-  <si>
-    <t>0.4929,0.5980,0.0703,0.0013</t>
-  </si>
-  <si>
-    <t>0.9188,0.0492,0.0159,0.0013</t>
-  </si>
-  <si>
-    <t>0.7815,0.2602,0.0348,0.0012</t>
-  </si>
-  <si>
-    <t>0.9429,0.0235,0.0171,0.0016</t>
-  </si>
-  <si>
-    <t>0.7582,0.0676,0.0368,0.0329</t>
-  </si>
-  <si>
-    <t>0.8468,0.0621,0.0227,0.0066</t>
-  </si>
-  <si>
-    <t>0.8910,0.0157,0.0109,0.0154</t>
-  </si>
-  <si>
-    <t>0.8284,0.0515,0.0468,0.0132</t>
-  </si>
-  <si>
-    <t>0.7873,0.1050,0.0459,0.0120</t>
-  </si>
-  <si>
-    <t>0.7055,0.2525,0.0457,0.0070</t>
-  </si>
-  <si>
-    <t>0.7102,0.1404,0.0567,0.0142</t>
-  </si>
-  <si>
-    <t>0.7153,0.0679,0.1725,0.0001</t>
-  </si>
-  <si>
-    <t>0.9686,0.0121,0.0091,0.0001</t>
-  </si>
-  <si>
-    <t>0.8753,0.0105,0.1160,0.0001</t>
-  </si>
-  <si>
-    <t>0.9839,0.0012,0.0113,0.0000</t>
-  </si>
-  <si>
-    <t>0.9746,0.0095,0.0086,0.0004</t>
-  </si>
-  <si>
-    <t>0.9313,0.0309,0.0291,0.0003</t>
-  </si>
-  <si>
-    <t>0.9304,0.0107,0.0504,0.0007</t>
-  </si>
-  <si>
-    <t>0.9587,0.0242,0.0128,0.0002</t>
-  </si>
-  <si>
-    <t>0.9371,0.0144,0.0287,0.0010</t>
-  </si>
-  <si>
-    <t>0.8481,0.0180,0.0213,0.0244</t>
-  </si>
-  <si>
-    <t>0.8974,0.0513,0.0234,0.0075</t>
-  </si>
-  <si>
-    <t>0.8296,0.0821,0.0579,0.0042</t>
-  </si>
-  <si>
-    <t>0.6617,0.1516,0.1535,0.0025</t>
-  </si>
-  <si>
-    <t>0.7642,0.1901,0.0396,0.0048</t>
-  </si>
-  <si>
-    <t>0.8871,0.0827,0.0324,0.0009</t>
-  </si>
-  <si>
-    <t>0.7676,0.0482,0.0258,0.0309</t>
-  </si>
-  <si>
-    <t>0.7344,0.2631,0.0443,0.0035</t>
-  </si>
-  <si>
-    <t>0.8419,0.1068,0.0525,0.0036</t>
-  </si>
-  <si>
-    <t>0.6126,0.2620,0.0487,0.0093</t>
-  </si>
-  <si>
-    <t>0.6507,0.0730,0.0328,0.0477</t>
-  </si>
-  <si>
-    <t>0.1388,0.5279,0.7304,0.0108</t>
-  </si>
-  <si>
-    <t>0.6354,0.1286,0.0640,0.0450</t>
-  </si>
-  <si>
-    <t>0.7564,0.1403,0.0541,0.0086</t>
-  </si>
-  <si>
-    <t>0.8464,0.1519,0.0203,0.0012</t>
-  </si>
-  <si>
-    <t>0.8822,0.0917,0.0194,0.0011</t>
-  </si>
-  <si>
-    <t>0.9149,0.0519,0.0294,0.0011</t>
-  </si>
-  <si>
-    <t>0.4526,0.5105,0.1186,0.0097</t>
-  </si>
-  <si>
-    <t>0.8724,0.1270,0.0202,0.0017</t>
-  </si>
-  <si>
-    <t>0.9435,0.0339,0.0104,0.0007</t>
-  </si>
-  <si>
-    <t>0.7263,0.1706,0.0418,0.0078</t>
-  </si>
-  <si>
-    <t>0.7826,0.1522,0.0364,0.0048</t>
-  </si>
-  <si>
-    <t>0.7683,0.0575,0.0421,0.0301</t>
-  </si>
-  <si>
-    <t>0.8189,0.0730,0.0415,0.0109</t>
-  </si>
-  <si>
-    <t>0.8180,0.0824,0.0362,0.0075</t>
-  </si>
-  <si>
-    <t>0.7939,0.0887,0.0770,0.0088</t>
-  </si>
-  <si>
-    <t>0.7940,0.1245,0.0397,0.0104</t>
-  </si>
-  <si>
-    <t>0.7022,0.2163,0.0419,0.0084</t>
-  </si>
-  <si>
-    <t>0.6525,0.3649,0.0640,0.0032</t>
-  </si>
-  <si>
-    <t>0.5981,0.3174,0.0709,0.0131</t>
-  </si>
-  <si>
-    <t>0.8495,0.1213,0.0365,0.0015</t>
-  </si>
-  <si>
-    <t>0.8271,0.1053,0.0315,0.0048</t>
-  </si>
-  <si>
-    <t>0.6765,0.2097,0.0777,0.0146</t>
-  </si>
-  <si>
-    <t>0.8736,0.0349,0.0321,0.0075</t>
-  </si>
-  <si>
-    <t>0.6943,0.1301,0.0564,0.0174</t>
-  </si>
-  <si>
-    <t>0.7079,0.1779,0.0799,0.0113</t>
-  </si>
-  <si>
-    <t>0.3014,0.0824,0.8037,0.0013</t>
-  </si>
-  <si>
-    <t>0.8062,0.0938,0.0476,0.0064</t>
-  </si>
-  <si>
-    <t>0.9304,0.0041,0.0653,0.0002</t>
-  </si>
-  <si>
-    <t>0.9593,0.0027,0.0460,0.0001</t>
-  </si>
-  <si>
-    <t>0.8896,0.0129,0.1000,0.0007</t>
-  </si>
-  <si>
-    <t>0.5313,0.0318,0.5226,0.0005</t>
-  </si>
-  <si>
-    <t>0.9256,0.0222,0.0503,0.0003</t>
-  </si>
-  <si>
-    <t>0.7698,0.0123,0.2633,0.0002</t>
-  </si>
-  <si>
-    <t>0.7553,0.0135,0.3631,0.0007</t>
-  </si>
-  <si>
-    <t>0.9447,0.0178,0.0263,0.0008</t>
-  </si>
-  <si>
-    <t>0.9382,0.0203,0.0360,0.0003</t>
-  </si>
-  <si>
-    <t>0.9446,0.0202,0.0185,0.0005</t>
-  </si>
-  <si>
-    <t>0.9243,0.0381,0.0289,0.0004</t>
-  </si>
-  <si>
-    <t>0.7143,0.1551,0.1701,0.0026</t>
-  </si>
-  <si>
-    <t>0.9594,0.0187,0.0173,0.0002</t>
-  </si>
-  <si>
-    <t>0.8044,0.1127,0.0761,0.0022</t>
-  </si>
-  <si>
-    <t>0.9235,0.0384,0.0240,0.0003</t>
-  </si>
-  <si>
-    <t>0.8395,0.1133,0.0397,0.0019</t>
-  </si>
-  <si>
-    <t>0.6694,0.3753,0.0460,0.0035</t>
-  </si>
-  <si>
-    <t>0.6345,0.3526,0.0662,0.0050</t>
-  </si>
-  <si>
-    <t>0.6550,0.1265,0.0349,0.0226</t>
-  </si>
-  <si>
-    <t>0.4902,0.5427,0.0677,0.0035</t>
-  </si>
-  <si>
-    <t>0.9790,0.0109,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.9431,0.0513,0.0100,0.0001</t>
-  </si>
-  <si>
-    <t>0.9706,0.0098,0.0115,0.0002</t>
-  </si>
-  <si>
-    <t>0.8806,0.0617,0.0553,0.0003</t>
-  </si>
-  <si>
-    <t>0.9676,0.0041,0.0175,0.0002</t>
-  </si>
-  <si>
-    <t>0.8711,0.0229,0.1257,0.0009</t>
-  </si>
-  <si>
-    <t>0.9486,0.0233,0.0135,0.0001</t>
-  </si>
-  <si>
-    <t>0.9684,0.0078,0.0138,0.0002</t>
-  </si>
-  <si>
-    <t>0.9756,0.0019,0.0131,0.0001</t>
-  </si>
-  <si>
-    <t>0.8855,0.0286,0.0517,0.0002</t>
-  </si>
-  <si>
-    <t>0.7265,0.1716,0.0605,0.0071</t>
-  </si>
-  <si>
-    <t>0.7360,0.0702,0.0514,0.0293</t>
-  </si>
-  <si>
-    <t>0.7377,0.0963,0.0907,0.0227</t>
-  </si>
-  <si>
-    <t>0.8006,0.0650,0.0436,0.0151</t>
-  </si>
-  <si>
-    <t>0.6055,0.2686,0.0964,0.0104</t>
-  </si>
-  <si>
-    <t>0.7957,0.0753,0.0231,0.0119</t>
-  </si>
-  <si>
-    <t>0.8791,0.0371,0.0170,0.0070</t>
-  </si>
-  <si>
-    <t>0.8315,0.0640,0.0258,0.0076</t>
-  </si>
-  <si>
-    <t>0.8432,0.0965,0.0833,0.0010</t>
-  </si>
-  <si>
-    <t>0.8124,0.1548,0.0477,0.0018</t>
-  </si>
-  <si>
-    <t>0.8355,0.1153,0.0473,0.0029</t>
-  </si>
-  <si>
-    <t>0.9504,0.0030,0.0537,0.0001</t>
-  </si>
-  <si>
-    <t>0.7696,0.0128,0.2566,0.0027</t>
-  </si>
-  <si>
-    <t>0.8684,0.0804,0.0237,0.0002</t>
-  </si>
-  <si>
-    <t>0.8636,0.0051,0.2286,0.0003</t>
-  </si>
-  <si>
-    <t>0.9131,0.0124,0.0948,0.0002</t>
-  </si>
-  <si>
-    <t>0.8181,0.0014,0.3122,0.0003</t>
-  </si>
-  <si>
-    <t>0.9319,0.0052,0.0505,0.0003</t>
-  </si>
-  <si>
-    <t>0.9733,0.0113,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.9094,0.0440,0.0377,0.0008</t>
-  </si>
-  <si>
-    <t>0.9655,0.0081,0.0200,0.0003</t>
-  </si>
-  <si>
-    <t>0.9805,0.0182,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.8240,0.0369,0.0310,0.0187</t>
-  </si>
-  <si>
-    <t>0.6443,0.0603,0.0284,0.0584</t>
-  </si>
-  <si>
-    <t>0.8539,0.0447,0.0328,0.0074</t>
-  </si>
-  <si>
-    <t>0.6658,0.1078,0.0439,0.0329</t>
-  </si>
-  <si>
-    <t>0.7813,0.0333,0.0180,0.0330</t>
-  </si>
-  <si>
-    <t>0.7497,0.0788,0.0358,0.0195</t>
-  </si>
-  <si>
-    <t>0.6853,0.0865,0.0640,0.0406</t>
-  </si>
-  <si>
-    <t>0.5956,0.1781,0.0566,0.0358</t>
-  </si>
-  <si>
-    <t>0.9403,0.0041,0.0639,0.0001</t>
-  </si>
-  <si>
-    <t>0.9428,0.0063,0.0520,0.0001</t>
-  </si>
-  <si>
-    <t>0.7197,0.0081,0.4279,0.0003</t>
-  </si>
-  <si>
-    <t>0.9421,0.0184,0.0246,0.0007</t>
-  </si>
-  <si>
-    <t>0.8618,0.0064,0.2130,0.0003</t>
-  </si>
-  <si>
-    <t>0.9765,0.0057,0.0099,0.0003</t>
-  </si>
-  <si>
-    <t>0.9688,0.0032,0.0264,0.0000</t>
-  </si>
-  <si>
-    <t>0.9618,0.0110,0.0174,0.0003</t>
-  </si>
-  <si>
-    <t>0.9079,0.0187,0.0240,0.0059</t>
-  </si>
-  <si>
-    <t>0.9624,0.0097,0.0121,0.0009</t>
-  </si>
-  <si>
-    <t>0.9392,0.0181,0.0078,0.0035</t>
-  </si>
-  <si>
-    <t>0.8914,0.0216,0.0277,0.0089</t>
-  </si>
-  <si>
-    <t>0.8807,0.0120,0.0121,0.0316</t>
-  </si>
-  <si>
-    <t>0.7959,0.0908,0.0519,0.0097</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9247,0.0145,0.0063,0.0386</t>
+  </si>
+  <si>
+    <t>0.0496,0.0002,0.0001,0.9902</t>
+  </si>
+  <si>
+    <t>0.9784,0.0041,0.0015,0.0100</t>
+  </si>
+  <si>
+    <t>0.0295,0.0054,0.0062,0.9805</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0009,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0029,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9917,0.0082,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9961,0.0016,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.8615,0.0708,0.0610,0.0039</t>
+  </si>
+  <si>
+    <t>0.1146,0.0198,0.9305,0.0019</t>
+  </si>
+  <si>
+    <t>0.4233,0.0181,0.7465,0.0059</t>
+  </si>
+  <si>
+    <t>0.0155,0.3098,0.6753,0.0063</t>
+  </si>
+  <si>
+    <t>0.9345,0.0254,0.0237,0.0014</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.9983,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.1011,0.9281,0.0065,0.0005</t>
+  </si>
+  <si>
+    <t>0.0035,0.9944,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9950,0.0023,0.0015</t>
+  </si>
+  <si>
+    <t>0.6356,0.0035,0.2712,0.0369</t>
+  </si>
+  <si>
+    <t>0.3595,0.0226,0.5296,0.0694</t>
+  </si>
+  <si>
+    <t>0.0142,0.0029,0.9859,0.0051</t>
+  </si>
+  <si>
+    <t>0.1109,0.0161,0.9117,0.0252</t>
+  </si>
+  <si>
+    <t>0.4683,0.0031,0.6850,0.0016</t>
+  </si>
+  <si>
+    <t>0.0501,0.0034,0.9637,0.0122</t>
+  </si>
+  <si>
+    <t>0.0033,0.0084,0.9926,0.0026</t>
+  </si>
+  <si>
+    <t>0.2808,0.8654,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.1999,0.3703,0.5690,0.0164</t>
+  </si>
+  <si>
+    <t>0.0096,0.0198,0.9815,0.0144</t>
+  </si>
+  <si>
+    <t>0.0298,0.8789,0.1097,0.0004</t>
+  </si>
+  <si>
+    <t>0.7110,0.0384,0.0374,0.1773</t>
+  </si>
+  <si>
+    <t>0.7497,0.0169,0.2538,0.0119</t>
+  </si>
+  <si>
+    <t>0.7911,0.3260,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.0205,0.9754,0.1644,0.0006</t>
+  </si>
+  <si>
+    <t>0.0061,0.7997,0.1783,0.1600</t>
+  </si>
+  <si>
+    <t>0.0303,0.0054,0.9767,0.0032</t>
+  </si>
+  <si>
+    <t>0.1243,0.2580,0.7415,0.0342</t>
+  </si>
+  <si>
+    <t>0.4185,0.0013,0.7397,0.0019</t>
+  </si>
+  <si>
+    <t>0.0111,0.0567,0.9827,0.0023</t>
+  </si>
+  <si>
+    <t>0.0076,0.9859,0.0100,0.0007</t>
+  </si>
+  <si>
+    <t>0.0089,0.0034,0.9914,0.0020</t>
+  </si>
+  <si>
+    <t>0.0443,0.7875,0.0047,0.5332</t>
+  </si>
+  <si>
+    <t>0.0105,0.9784,0.0170,0.0109</t>
+  </si>
+  <si>
+    <t>0.0023,0.9956,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9970,0.0084,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.1381,0.9587,0.0113</t>
+  </si>
+  <si>
+    <t>0.0058,0.2114,0.9773,0.0021</t>
+  </si>
+  <si>
+    <t>0.4816,0.0119,0.6409,0.0043</t>
+  </si>
+  <si>
+    <t>0.1721,0.0121,0.8975,0.0071</t>
+  </si>
+  <si>
+    <t>0.0344,0.0249,0.9584,0.0084</t>
+  </si>
+  <si>
+    <t>0.1248,0.0623,0.8661,0.0211</t>
+  </si>
+  <si>
+    <t>0.9360,0.1242,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9889,0.0088,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.9780,0.0184,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.0185,0.2010,0.9693,0.0091</t>
+  </si>
+  <si>
+    <t>0.9965,0.0009,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9856,0.0149,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.9844,0.0136,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.0005,0.9473,0.9825,0.0002</t>
+  </si>
+  <si>
+    <t>0.0273,0.2061,0.9104,0.0025</t>
+  </si>
+  <si>
+    <t>0.0426,0.0963,0.9409,0.0057</t>
+  </si>
+  <si>
+    <t>0.0001,0.9919,0.9787,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0138,0.9929,0.0039</t>
+  </si>
+  <si>
+    <t>0.0467,0.9357,0.0240,0.0039</t>
+  </si>
+  <si>
+    <t>0.0117,0.9894,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.7419,0.0064,0.2750,0.0229</t>
+  </si>
+  <si>
+    <t>0.2549,0.1169,0.7775,0.0083</t>
+  </si>
+  <si>
+    <t>0.0069,0.0084,0.9876,0.0150</t>
+  </si>
+  <si>
+    <t>0.0016,0.9632,0.7833,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.9550,0.5423,0.0002</t>
+  </si>
+  <si>
+    <t>0.0086,0.8707,0.4352,0.0011</t>
+  </si>
+  <si>
+    <t>0.0141,0.8933,0.6693,0.0037</t>
+  </si>
+  <si>
+    <t>0.0051,0.0006,0.0653,0.9804</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0071,0.0081,0.0003,0.9962</t>
+  </si>
+  <si>
+    <t>0.0109,0.0023,0.0024,0.9937</t>
+  </si>
+  <si>
+    <t>0.0094,0.0060,0.0039,0.9911</t>
+  </si>
+  <si>
+    <t>0.0044,0.0016,0.0007,0.9969</t>
+  </si>
+  <si>
+    <t>0.0011,0.9360,0.9391,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.2866,0.9802,0.0008</t>
+  </si>
+  <si>
+    <t>0.0035,0.9713,0.1370,0.0015</t>
+  </si>
+  <si>
+    <t>0.0048,0.5862,0.9302,0.0014</t>
+  </si>
+  <si>
+    <t>0.0010,0.9825,0.6420,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.9423,0.5938,0.0015</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.7229,0.5040,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9894,0.0113,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9900,0.0077,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9951,0.0025,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0061,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9971,0.0023,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9819,0.0199,0.0028,0.0010</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0022,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0018,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0000,0.0000,0.0020</t>
+  </si>
+  <si>
+    <t>0.0015,0.0009,0.9943,0.0082</t>
+  </si>
+  <si>
+    <t>0.1760,0.0049,0.9243,0.0044</t>
+  </si>
+  <si>
+    <t>0.9735,0.0012,0.0106,0.0020</t>
+  </si>
+  <si>
+    <t>0.1808,0.0025,0.9165,0.0024</t>
+  </si>
+  <si>
+    <t>0.0187,0.9752,0.0029,0.0021</t>
+  </si>
+  <si>
+    <t>0.0069,0.9898,0.0050,0.0008</t>
+  </si>
+  <si>
+    <t>0.0094,0.9852,0.0024,0.0026</t>
+  </si>
+  <si>
+    <t>0.0064,0.9884,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.0006,0.9981,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.5641,0.6099,0.0052,0.0006</t>
+  </si>
+  <si>
+    <t>0.8284,0.0114,0.1485,0.0137</t>
+  </si>
+  <si>
+    <t>0.2381,0.0347,0.8147,0.0032</t>
+  </si>
+  <si>
+    <t>0.4965,0.0642,0.2901,0.0806</t>
+  </si>
+  <si>
+    <t>0.8536,0.1057,0.0171,0.0073</t>
+  </si>
+  <si>
+    <t>0.0335,0.2359,0.1634,0.8464</t>
+  </si>
+  <si>
+    <t>0.0023,0.9961,0.0112,0.0004</t>
+  </si>
+  <si>
+    <t>0.0017,0.9950,0.0083,0.0014</t>
+  </si>
+  <si>
+    <t>0.0003,0.9980,0.0012,0.0030</t>
+  </si>
+  <si>
+    <t>0.0043,0.9797,0.4300,0.0012</t>
+  </si>
+  <si>
+    <t>0.0027,0.9959,0.0129,0.0001</t>
+  </si>
+  <si>
+    <t>0.8685,0.1408,0.0300,0.0016</t>
+  </si>
+  <si>
+    <t>0.9505,0.0611,0.0057,0.0013</t>
+  </si>
+  <si>
+    <t>0.9901,0.0060,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9958,0.0005,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9940,0.0020,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9894,0.0053,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.9946,0.0008,0.0003,0.0031</t>
+  </si>
+  <si>
+    <t>0.9840,0.0180,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9933,0.0011,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9949,0.0028,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9881,0.2442,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.8922,0.9645,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.1119,0.9889,0.0002</t>
+  </si>
+  <si>
+    <t>0.0483,0.0043,0.9746,0.0026</t>
+  </si>
+  <si>
+    <t>0.9884,0.0046,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.9122,0.0062,0.0872,0.0047</t>
+  </si>
+  <si>
+    <t>0.1895,0.0034,0.8385,0.0344</t>
+  </si>
+  <si>
+    <t>0.8907,0.0294,0.0465,0.0129</t>
+  </si>
+  <si>
+    <t>0.0495,0.0025,0.0047,0.9757</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0062,0.0039,0.0028,0.9949</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.0006,0.9993</t>
+  </si>
+  <si>
+    <t>0.0186,0.4287,0.8765,0.0160</t>
+  </si>
+  <si>
+    <t>0.9937,0.0010,0.0006,0.0018</t>
+  </si>
+  <si>
+    <t>0.0421,0.9518,0.0052,0.0097</t>
+  </si>
+  <si>
+    <t>0.9781,0.0027,0.0042,0.0091</t>
+  </si>
+  <si>
+    <t>0.1070,0.9324,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9913,0.0024,0.0007,0.0025</t>
+  </si>
+  <si>
+    <t>0.8132,0.0060,0.0503,0.0841</t>
+  </si>
+  <si>
+    <t>0.9842,0.0025,0.0013,0.0068</t>
+  </si>
+  <si>
+    <t>0.0024,0.2359,0.8709,0.1356</t>
+  </si>
+  <si>
+    <t>0.5131,0.0002,0.0002,0.7865</t>
+  </si>
+  <si>
+    <t>0.7869,0.0044,0.0052,0.2161</t>
+  </si>
+  <si>
+    <t>0.2830,0.7396,0.0253,0.0117</t>
+  </si>
+  <si>
+    <t>0.8827,0.1049,0.0150,0.0072</t>
+  </si>
+  <si>
+    <t>0.9297,0.0617,0.0153,0.0057</t>
+  </si>
+  <si>
+    <t>0.3637,0.5268,0.0312,0.0136</t>
+  </si>
+  <si>
+    <t>0.8503,0.0522,0.0696,0.0018</t>
+  </si>
+  <si>
+    <t>0.9854,0.0103,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9828,0.0090,0.0017,0.0040</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.9951,0.0012,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9903,0.0064,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9931,0.0022,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.7684,0.2769,0.0073,0.0021</t>
+  </si>
+  <si>
+    <t>0.5217,0.6639,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.5542,0.5812,0.0049,0.0009</t>
+  </si>
+  <si>
+    <t>0.4379,0.0902,0.6380,0.0112</t>
+  </si>
+  <si>
+    <t>0.9882,0.0094,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9840,0.0060,0.0016,0.0028</t>
+  </si>
+  <si>
+    <t>0.9912,0.0061,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9884,0.0081,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.0073,0.0353,0.9940,0.0009</t>
+  </si>
+  <si>
+    <t>0.9772,0.0322,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.0052,0.0034,0.9868,0.0131</t>
+  </si>
+  <si>
+    <t>0.0441,0.0369,0.9496,0.0108</t>
+  </si>
+  <si>
+    <t>0.0082,0.0021,0.9904,0.0063</t>
+  </si>
+  <si>
+    <t>0.0046,0.0441,0.9871,0.0035</t>
+  </si>
+  <si>
+    <t>0.0144,0.0227,0.9850,0.0013</t>
+  </si>
+  <si>
+    <t>0.0169,0.0007,0.9916,0.0011</t>
+  </si>
+  <si>
+    <t>0.0026,0.0063,0.9947,0.0041</t>
+  </si>
+  <si>
+    <t>0.0483,0.0097,0.9699,0.0025</t>
+  </si>
+  <si>
+    <t>0.1551,0.1023,0.7996,0.0114</t>
+  </si>
+  <si>
+    <t>0.3988,0.1979,0.5008,0.0614</t>
+  </si>
+  <si>
+    <t>0.1859,0.0439,0.8014,0.0030</t>
+  </si>
+  <si>
+    <t>0.1869,0.0422,0.7796,0.0026</t>
+  </si>
+  <si>
+    <t>0.7712,0.0586,0.1747,0.0059</t>
+  </si>
+  <si>
+    <t>0.4104,0.5006,0.0777,0.0034</t>
+  </si>
+  <si>
+    <t>0.0377,0.0089,0.9768,0.0044</t>
+  </si>
+  <si>
+    <t>0.0039,0.9934,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.0095,0.9918,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.8136,0.3166,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9778,0.0383,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.5265,0.6183,0.0026,0.0022</t>
+  </si>
+  <si>
+    <t>0.9280,0.0373,0.0183,0.0016</t>
+  </si>
+  <si>
+    <t>0.9823,0.0037,0.0069,0.0012</t>
+  </si>
+  <si>
+    <t>0.7739,0.0089,0.0202,0.1558</t>
+  </si>
+  <si>
+    <t>0.8927,0.0019,0.1716,0.0003</t>
+  </si>
+  <si>
+    <t>0.7518,0.0053,0.1015,0.0630</t>
+  </si>
+  <si>
+    <t>0.0391,0.0061,0.9644,0.0125</t>
+  </si>
+  <si>
+    <t>0.0864,0.4266,0.7251,0.0236</t>
+  </si>
+  <si>
+    <t>0.0162,0.0073,0.9705,0.0149</t>
+  </si>
+  <si>
+    <t>0.0551,0.0103,0.9499,0.0086</t>
+  </si>
+  <si>
+    <t>0.0489,0.0935,0.8899,0.0187</t>
+  </si>
+  <si>
+    <t>0.9858,0.0030,0.0002,0.0049</t>
+  </si>
+  <si>
+    <t>0.9942,0.0024,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9695,0.0218,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9949,0.0043,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9854,0.0108,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9954,0.0022,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9914,0.0053,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.0964,0.0330,0.9354,0.0104</t>
+  </si>
+  <si>
+    <t>0.1533,0.7894,0.2179,0.0105</t>
+  </si>
+  <si>
+    <t>0.9292,0.0139,0.0440,0.0040</t>
+  </si>
+  <si>
+    <t>0.0185,0.0043,0.9730,0.0227</t>
+  </si>
+  <si>
+    <t>0.0078,0.0108,0.9539,0.0832</t>
+  </si>
+  <si>
+    <t>0.1234,0.1516,0.8038,0.0082</t>
+  </si>
+  <si>
+    <t>0.0210,0.0057,0.9846,0.0017</t>
+  </si>
+  <si>
+    <t>0.1027,0.0327,0.9104,0.0080</t>
+  </si>
+  <si>
+    <t>0.0012,0.0044,0.9948,0.0047</t>
+  </si>
+  <si>
+    <t>0.0038,0.0209,0.9841,0.0091</t>
+  </si>
+  <si>
+    <t>0.1367,0.0729,0.7234,0.0039</t>
+  </si>
+  <si>
+    <t>0.8954,0.0017,0.1331,0.0020</t>
+  </si>
+  <si>
+    <t>0.9323,0.0020,0.0743,0.0008</t>
+  </si>
+  <si>
+    <t>0.9271,0.0208,0.0062,0.0181</t>
+  </si>
+  <si>
+    <t>0.9879,0.0098,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9955,0.0013,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9735,0.0368,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9910,0.0140,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9918,0.0097,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0356,0.1627,0.8582,0.0085</t>
+  </si>
+  <si>
+    <t>0.0042,0.2665,0.9653,0.0035</t>
+  </si>
+  <si>
+    <t>0.0039,0.0072,0.9917,0.0033</t>
+  </si>
+  <si>
+    <t>0.0550,0.0147,0.9401,0.0044</t>
+  </si>
+  <si>
+    <t>0.0576,0.0027,0.9709,0.0008</t>
+  </si>
+  <si>
+    <t>0.7367,0.0109,0.1624,0.0562</t>
+  </si>
+  <si>
+    <t>0.1270,0.0121,0.9079,0.0082</t>
+  </si>
+  <si>
+    <t>0.3557,0.0201,0.5875,0.0491</t>
+  </si>
+  <si>
+    <t>0.5852,0.0012,0.0050,0.5590</t>
+  </si>
+  <si>
+    <t>0.0198,0.0083,0.0003,0.9891</t>
+  </si>
+  <si>
+    <t>0.0268,0.0006,0.0008,0.9910</t>
+  </si>
+  <si>
+    <t>0.0025,0.0002,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.0147,0.0009,0.0005,0.9949</t>
+  </si>
+  <si>
+    <t>0.9221,0.0173,0.0065,0.0359</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,10 +2194,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,10 +3188,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,10 +3524,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4126,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4661,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,10 +5106,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,10 +5134,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
